--- a/0_SELECT_ZIVE_DATA_2023/06_Anotacijos_logai/06_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/06_Anotacijos_logai/06_Anotavimo_logas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\1_PREPARE_TRAIN_UNET_DATA\TriuksmaiAnotacijosDuomenyse2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\06_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE29295-80BC-47B7-8941-9B63573B98F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6D4A00-7BB8-4876-8D62-5BBD0ECE9293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sarasas" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="91">
   <si>
     <t>filename</t>
   </si>
@@ -58,9 +58,6 @@
     <t>tag</t>
   </si>
   <si>
-    <t>N,J,Ž</t>
-  </si>
-  <si>
     <t>mark</t>
   </si>
   <si>
@@ -94,18 +91,12 @@
     <t>h_nz_len</t>
   </si>
   <si>
-    <t>h_nz_frac</t>
-  </si>
-  <si>
     <t>ml_nz_cnt</t>
   </si>
   <si>
     <t>ml_nz_len</t>
   </si>
   <si>
-    <t>ml_nz_frac</t>
-  </si>
-  <si>
     <t>flags</t>
   </si>
   <si>
@@ -115,30 +106,15 @@
     <t>userId</t>
   </si>
   <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>1000_1</t>
-  </si>
-  <si>
-    <t>1626941.468</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
-    <t>EXTERNALLY_ANNOTATED,FOR_EXTERNAL_ANNOTATING,PSEUDO_ANNOTATED</t>
-  </si>
-  <si>
     <t>60f945e187cf66e97e37810e</t>
   </si>
   <si>
     <t>6034c808d6c2740008035ede</t>
   </si>
   <si>
-    <t>Truputi plaukioja amplitudė</t>
-  </si>
-  <si>
     <t>1001_3</t>
   </si>
   <si>
@@ -169,39 +145,18 @@
     <t>Neaišku, kas yra ties 12300 klausimas gydytojui. Gal verta užblokuoti 3 pūpsnius pradedant reikšme 68100, gal dar 2 - ties 92700, nors dabartiniam ML nepakenkė</t>
   </si>
   <si>
-    <t>1008_11</t>
-  </si>
-  <si>
-    <t>1630812.584</t>
-  </si>
-  <si>
     <t>613f585a3d08d49213cdcd47</t>
   </si>
   <si>
     <t>613b1d0c3d08d413ffcdc8f6</t>
   </si>
   <si>
-    <t>Švarus</t>
-  </si>
-  <si>
-    <t>1009_0</t>
-  </si>
-  <si>
-    <t>1631141.137</t>
-  </si>
-  <si>
     <t>613b22d53d08d4ea5fcdc9ec</t>
   </si>
   <si>
     <t>613b1d673d08d4d1f3cdc8f8</t>
   </si>
   <si>
-    <t>1019_54</t>
-  </si>
-  <si>
-    <t>1631089.859</t>
-  </si>
-  <si>
     <t>*</t>
   </si>
   <si>
@@ -211,9 +166,6 @@
     <t>6144c682bd0cc5acb7275368</t>
   </si>
   <si>
-    <t>truputis triukšmo</t>
-  </si>
-  <si>
     <t>1030_5</t>
   </si>
   <si>
@@ -229,72 +181,12 @@
     <t>geras</t>
   </si>
   <si>
-    <t>1030_29</t>
-  </si>
-  <si>
-    <t>1633432.319</t>
-  </si>
-  <si>
     <t>61632c1f1e3255590d017c2f</t>
   </si>
   <si>
-    <t>1030_31</t>
-  </si>
-  <si>
-    <t>1633426.058</t>
-  </si>
-  <si>
-    <t>61632c1e1e32553c30017bc4</t>
-  </si>
-  <si>
-    <t>1035_8</t>
-  </si>
-  <si>
-    <t>1633405.853</t>
-  </si>
-  <si>
-    <t>61632e6f1e3255e22e01807f</t>
-  </si>
-  <si>
-    <t>61632bd41e32554ace017bc0</t>
-  </si>
-  <si>
-    <t>yra triukšmų, yra V. Raumenų triukšmo segmentas , nuo 43800, 5 pūpsniai, nuo 49400 - 4 pūpsniai, nuo 86400 - 7 pūpsniai</t>
-  </si>
-  <si>
-    <t>1035_50</t>
-  </si>
-  <si>
-    <t>1633328.044</t>
-  </si>
-  <si>
-    <t>61632e6f1e3255838901803e</t>
-  </si>
-  <si>
-    <t>Kokybė artima 10, vietomis nedidelis BW, keleta epizodų su EMG</t>
-  </si>
-  <si>
-    <t>1100_0</t>
-  </si>
-  <si>
-    <t>1646116.344</t>
-  </si>
-  <si>
-    <t>622e3a2f3c70e6065e8a2d7b</t>
-  </si>
-  <si>
-    <t>622dfee93c70e6c8798a21af</t>
-  </si>
-  <si>
-    <t>idealus, S didesnis už Q</t>
-  </si>
-  <si>
     <t>nr</t>
   </si>
   <si>
-    <t>file_name</t>
-  </si>
-  <si>
     <t>Anotatorius</t>
   </si>
   <si>
@@ -316,22 +208,120 @@
     <t>uid</t>
   </si>
   <si>
-    <t>Žygimantas</t>
-  </si>
-  <si>
-    <t>Vietomis nedidelis virpėjimas, galimas demo Nikai</t>
-  </si>
-  <si>
     <t>Po anotacijos</t>
+  </si>
+  <si>
+    <t>cmt</t>
+  </si>
+  <si>
+    <t>h_nz_frac%</t>
+  </si>
+  <si>
+    <t>ml_nz_frac%</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>1001_7</t>
+  </si>
+  <si>
+    <t>1670177.65</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>638d8e519e4d43245abbb0c5</t>
+  </si>
+  <si>
+    <t>1006_2</t>
+  </si>
+  <si>
+    <t>1630813.935</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>613f59533d08d4e57fcdced5</t>
+  </si>
+  <si>
+    <t>613b1c9c3d08d43181cdc8f4</t>
+  </si>
+  <si>
+    <t>Yra keletas epizodų su BW, EMG, EMA</t>
+  </si>
+  <si>
+    <t>1006_3</t>
+  </si>
+  <si>
+    <t>1630808.306</t>
+  </si>
+  <si>
+    <t>613f59533d08d47abacdcecc</t>
+  </si>
+  <si>
+    <t>Yra keletas epizodų su BW šuoliu</t>
+  </si>
+  <si>
+    <t>1001_2</t>
+  </si>
+  <si>
+    <t>1626924.927</t>
+  </si>
+  <si>
+    <t>60f9188487cf669c7e3780b8</t>
+  </si>
+  <si>
+    <t>izolinija šokinėja nedaug, vietomis išlenda raumenų triušmai</t>
+  </si>
+  <si>
+    <t>1002_1</t>
+  </si>
+  <si>
+    <t>1625402.027</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>60e1db5a93b55b56919e9ec0</t>
+  </si>
+  <si>
+    <t>60e1d80f93b55b41529e9eaa</t>
+  </si>
+  <si>
+    <t>izolinija vaikšto nedaug, vietomis išlenda raumenų triušmai, 13 V, bet atpažino tik 5, 8 min.</t>
+  </si>
+  <si>
+    <t>Nika</t>
+  </si>
+  <si>
+    <t>1009_1</t>
+  </si>
+  <si>
+    <t>1631141.764</t>
+  </si>
+  <si>
+    <t>AI_DATASET,FULLY_ANNOTATED_PROFESSIONALLY</t>
+  </si>
+  <si>
+    <t>613b22d53d08d4fe94cdc9ed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labai geras </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -359,7 +349,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -372,8 +362,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -396,11 +392,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -425,6 +430,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,12 +732,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="8" width="8" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
@@ -724,166 +751,180 @@
     <col min="26" max="26" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="T1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="W1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="X1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Y1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2">
+        <v>128000</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2222</v>
+      </c>
+      <c r="H2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="15">
+        <v>801</v>
+      </c>
+      <c r="J2" s="15">
+        <v>798</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>2</v>
+      </c>
+      <c r="R2">
+        <v>440</v>
+      </c>
+      <c r="S2" s="16">
+        <v>0.34375</v>
+      </c>
+      <c r="T2" s="15">
+        <v>0</v>
+      </c>
+      <c r="U2" s="15">
+        <v>0</v>
+      </c>
+      <c r="V2" s="17">
+        <v>0</v>
+      </c>
+      <c r="W2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="13"/>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2">
-        <v>127999</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2">
-        <v>861</v>
-      </c>
-      <c r="J2">
-        <v>859</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2" s="2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2" s="7">
-        <v>0</v>
-      </c>
-      <c r="W2" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>33</v>
       </c>
       <c r="B3">
         <v>127999</v>
       </c>
-      <c r="C3" t="s">
-        <v>34</v>
+      <c r="C3" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -891,13 +932,16 @@
       <c r="E3">
         <v>4</v>
       </c>
+      <c r="F3">
+        <v>2222</v>
+      </c>
       <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3">
+        <v>22</v>
+      </c>
+      <c r="I3" s="15">
         <v>869</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="15">
         <v>865</v>
       </c>
       <c r="K3">
@@ -910,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -924,55 +968,63 @@
       <c r="R3">
         <v>8200</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="16">
         <v>6.4063000492191353</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" s="7">
+      <c r="T3" s="15">
+        <v>0</v>
+      </c>
+      <c r="U3" s="15">
+        <v>0</v>
+      </c>
+      <c r="V3" s="17">
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="X3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Y3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="13"/>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B4">
         <v>127999</v>
       </c>
-      <c r="C4" t="s">
-        <v>40</v>
+      <c r="C4" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>3333</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4">
-        <v>806</v>
-      </c>
-      <c r="J4">
-        <v>805</v>
+        <v>67</v>
+      </c>
+      <c r="I4" s="15">
+        <v>675</v>
+      </c>
+      <c r="J4" s="15">
+        <v>674</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -984,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -993,63 +1045,74 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>4480</v>
-      </c>
-      <c r="S4" s="2">
-        <v>3.5000273439636249</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" s="7">
+        <v>11200</v>
+      </c>
+      <c r="S4" s="16">
+        <v>8.7500683599090614</v>
+      </c>
+      <c r="T4" s="15">
+        <v>0</v>
+      </c>
+      <c r="U4" s="15">
+        <v>0</v>
+      </c>
+      <c r="V4" s="17">
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="X4" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="Y4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="Z4" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="13"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>127999</v>
       </c>
-      <c r="C5" t="s">
-        <v>44</v>
+      <c r="C5" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>2222</v>
+      </c>
       <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5">
-        <v>676</v>
-      </c>
-      <c r="J5">
-        <v>667</v>
+        <v>22</v>
+      </c>
+      <c r="I5" s="15">
+        <v>806</v>
+      </c>
+      <c r="J5" s="15">
+        <v>805</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -1058,63 +1121,77 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" s="7">
+        <v>4480</v>
+      </c>
+      <c r="S5" s="16">
+        <v>3.5000273439636249</v>
+      </c>
+      <c r="T5" s="15">
+        <v>0</v>
+      </c>
+      <c r="U5" s="15">
+        <v>0</v>
+      </c>
+      <c r="V5" s="17">
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="X5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="Y5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="Z5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="13"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="B6">
         <v>127999</v>
       </c>
-      <c r="C6" t="s">
-        <v>49</v>
+      <c r="C6" s="14" t="s">
+        <v>72</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
-      <c r="I6">
-        <v>740</v>
-      </c>
-      <c r="J6">
-        <v>719</v>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>3333</v>
+      </c>
+      <c r="H6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="15">
+        <v>637</v>
+      </c>
+      <c r="J6" s="15">
+        <v>637</v>
       </c>
       <c r="K6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1123,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1132,60 +1209,74 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="7">
+        <v>4300</v>
+      </c>
+      <c r="S6" s="16">
+        <v>3.3594012453222293</v>
+      </c>
+      <c r="T6" s="15">
+        <v>0</v>
+      </c>
+      <c r="U6" s="15">
+        <v>0</v>
+      </c>
+      <c r="V6" s="17">
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="X6" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="Y6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="Z6" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>127999</v>
       </c>
-      <c r="C7" t="s">
-        <v>53</v>
+      <c r="C7" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>1111</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7">
-        <v>929</v>
-      </c>
-      <c r="J7">
-        <v>892</v>
+        <v>39</v>
+      </c>
+      <c r="I7" s="15">
+        <v>984</v>
+      </c>
+      <c r="J7" s="15">
+        <v>901</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="L7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -1194,81 +1285,86 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" s="7">
+        <v>4800</v>
+      </c>
+      <c r="S7" s="16">
+        <v>3.7500292971038838</v>
+      </c>
+      <c r="T7" s="15">
+        <v>0</v>
+      </c>
+      <c r="U7" s="15">
+        <v>0</v>
+      </c>
+      <c r="V7" s="17">
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="X7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Y7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="Z7" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B8">
         <v>127999</v>
       </c>
-      <c r="C8" t="s">
-        <v>59</v>
+      <c r="C8" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>1111</v>
+        <v>2222</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8">
-        <v>984</v>
-      </c>
-      <c r="J8">
-        <v>901</v>
+        <v>22</v>
+      </c>
+      <c r="I8" s="15">
+        <v>746</v>
+      </c>
+      <c r="J8" s="15">
+        <v>741</v>
       </c>
       <c r="K8">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1277,69 +1373,80 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R8">
-        <v>4800</v>
-      </c>
-      <c r="S8" s="2">
-        <v>3.7500292971038842</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" s="7">
+        <v>15698</v>
+      </c>
+      <c r="S8" s="16">
+        <v>12.264158313736825</v>
+      </c>
+      <c r="T8" s="15">
+        <v>0</v>
+      </c>
+      <c r="U8" s="15">
+        <v>0</v>
+      </c>
+      <c r="V8" s="17">
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="X8" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="Y8" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="Z8" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B9">
         <v>127999</v>
       </c>
-      <c r="C9" t="s">
-        <v>64</v>
+      <c r="C9" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>3333</v>
+      </c>
       <c r="H9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9">
-        <v>1022</v>
-      </c>
-      <c r="J9">
-        <v>997</v>
+        <v>81</v>
+      </c>
+      <c r="I9" s="15">
+        <v>765</v>
+      </c>
+      <c r="J9" s="15">
+        <v>748</v>
       </c>
       <c r="K9">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1348,134 +1455,74 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" s="7">
+        <v>26800</v>
+      </c>
+      <c r="S9" s="16">
+        <v>20.937663575496686</v>
+      </c>
+      <c r="T9" s="15">
+        <v>0</v>
+      </c>
+      <c r="U9" s="15">
+        <v>0</v>
+      </c>
+      <c r="V9" s="17">
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="X9" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="Y9" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10">
-        <v>127999</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10">
-        <v>904</v>
-      </c>
-      <c r="J10">
-        <v>886</v>
-      </c>
-      <c r="K10">
-        <v>17</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>17</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10" s="7">
-        <v>0</v>
-      </c>
-      <c r="W10" t="s">
-        <v>35</v>
-      </c>
-      <c r="X10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>69</v>
+        <v>83</v>
+      </c>
+      <c r="Z9" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A11" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="B11">
         <v>127999</v>
       </c>
-      <c r="C11" t="s">
-        <v>70</v>
+      <c r="C11" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11">
+        <v>1111</v>
+      </c>
       <c r="H11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11">
-        <v>667</v>
-      </c>
-      <c r="J11">
-        <v>658</v>
+        <v>67</v>
+      </c>
+      <c r="I11" s="15">
+        <v>865</v>
+      </c>
+      <c r="J11" s="15">
+        <v>845</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -1484,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="O11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1495,172 +1542,38 @@
       <c r="R11">
         <v>0</v>
       </c>
-      <c r="S11" s="2">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" s="7">
+      <c r="S11" s="16">
+        <v>0</v>
+      </c>
+      <c r="T11" s="15">
+        <v>0</v>
+      </c>
+      <c r="U11" s="15">
+        <v>0</v>
+      </c>
+      <c r="V11" s="17">
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="X11" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="Y11" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12">
-        <v>127999</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12">
-        <v>700</v>
-      </c>
-      <c r="J12">
-        <v>694</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>6</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>6</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12" s="7">
-        <v>0</v>
-      </c>
-      <c r="W12" t="s">
-        <v>35</v>
-      </c>
-      <c r="X12" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13">
-        <v>127999</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13">
-        <v>797</v>
-      </c>
-      <c r="J13">
-        <v>795</v>
-      </c>
-      <c r="K13">
-        <v>2</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>2</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13" s="7">
-        <v>0</v>
-      </c>
-      <c r="W13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X13" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>82</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="Z11" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="S12" s="2"/>
+      <c r="V12" s="7"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="S13" s="2"/>
+      <c r="V13" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Z1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1670,13 +1583,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
     <col min="5" max="5" width="24.36328125" customWidth="1"/>
     <col min="6" max="6" width="32.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -1691,46 +1604,46 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="E1" s="6" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -1745,33 +1658,32 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>92</v>
+        <v>61</v>
+      </c>
+      <c r="C2">
+        <v>128000</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5"/>
+      <c r="G2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
-      <c r="K2" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="K2" s="8"/>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
@@ -1779,26 +1691,32 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>127999</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
+      <c r="F3" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="K3" s="8"/>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="N3" t="str">
         <f>""</f>
@@ -1810,26 +1728,32 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="C4">
+        <v>127999</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>66</v>
+      </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
+      <c r="F4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="K4" s="8"/>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="N4" t="str">
         <f>""</f>
@@ -1841,26 +1765,32 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="C5">
+        <v>127999</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>32</v>
+      </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="5"/>
+      <c r="F5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="8" t="s">
-        <v>47</v>
-      </c>
+      <c r="K5" s="8"/>
       <c r="L5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="M5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="N5" t="str">
         <f>""</f>
@@ -1872,24 +1802,32 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="C6">
+        <v>127999</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="5"/>
+      <c r="F6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="8"/>
       <c r="L6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="M6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="N6" t="str">
         <f>""</f>
@@ -1901,30 +1839,32 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>92</v>
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>127999</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="5"/>
+      <c r="G7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="K7" s="8"/>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M7" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="N7" t="str">
         <f>""</f>
@@ -1936,26 +1876,32 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>127999</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="5"/>
+      <c r="F8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
-      <c r="K8" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="K8" s="8"/>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="M8" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="N8" t="str">
         <f>""</f>
@@ -1967,155 +1913,61 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="4"/>
+        <v>79</v>
+      </c>
+      <c r="C9">
+        <v>127999</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="5"/>
+      <c r="F9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="K9" s="8"/>
       <c r="L9" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="M9" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="N9" t="str">
         <f>""</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11" s="18">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="L10" t="s">
-        <v>68</v>
-      </c>
-      <c r="M10" t="s">
-        <v>61</v>
-      </c>
-      <c r="N10" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
       <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="5"/>
+      <c r="F11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
-      <c r="K11" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M11" t="s">
-        <v>72</v>
-      </c>
-      <c r="N11" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="L12" t="s">
-        <v>76</v>
-      </c>
-      <c r="M12" t="s">
-        <v>72</v>
-      </c>
-      <c r="N12" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="L13" t="s">
-        <v>80</v>
-      </c>
-      <c r="M13" t="s">
-        <v>81</v>
-      </c>
-      <c r="N13" t="str">
-        <f>""</f>
-        <v/>
-      </c>
+      <c r="K11" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
